--- a/database.xlsx
+++ b/database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Supply Chain\Gestão\Reportes\Relatório Mensal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662961B8-EBF3-47B1-B9C8-124CF1487BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F725F3-1A0C-4A62-9E09-4A1E98AA893C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{19CE77E3-4AC1-43FA-889F-0CF0F915B873}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19CE77E3-4AC1-43FA-889F-0CF0F915B873}"/>
   </bookViews>
   <sheets>
     <sheet name="Final" sheetId="1" r:id="rId1"/>
@@ -522,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D8CCE4-1984-402D-851F-C5F1CB7E5FA3}">
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2254,6 +2254,118 @@
         <v>2450</v>
       </c>
     </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>45931</v>
+      </c>
+      <c r="B35" s="3">
+        <v>875</v>
+      </c>
+      <c r="C35" s="3">
+        <v>1026.81</v>
+      </c>
+      <c r="D35" s="4">
+        <v>3105</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1352.94</v>
+      </c>
+      <c r="F35" s="3">
+        <v>597.01</v>
+      </c>
+      <c r="G35" s="3">
+        <v>639.47</v>
+      </c>
+      <c r="H35" s="3">
+        <v>2751</v>
+      </c>
+      <c r="I35" s="3">
+        <v>3950</v>
+      </c>
+      <c r="J35" s="3">
+        <v>5.42</v>
+      </c>
+      <c r="K35" s="3">
+        <v>5.3674090909090912</v>
+      </c>
+      <c r="L35" s="3">
+        <v>6.2997772727272743</v>
+      </c>
+      <c r="M35" s="5">
+        <v>0.7534045454545456</v>
+      </c>
+      <c r="N35" s="6">
+        <v>591.25</v>
+      </c>
+      <c r="O35" s="6">
+        <v>1830</v>
+      </c>
+      <c r="P35" s="6">
+        <v>2800</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>1800</v>
+      </c>
+      <c r="R35" s="6">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>45962</v>
+      </c>
+      <c r="B36" s="3">
+        <v>912.83</v>
+      </c>
+      <c r="C36" s="3">
+        <v>1064.5</v>
+      </c>
+      <c r="D36" s="4">
+        <v>2990</v>
+      </c>
+      <c r="E36" s="3">
+        <v>1312.08</v>
+      </c>
+      <c r="F36" s="3">
+        <v>551.64</v>
+      </c>
+      <c r="G36" s="3">
+        <v>642.86</v>
+      </c>
+      <c r="H36" s="3">
+        <v>2675</v>
+      </c>
+      <c r="I36" s="3">
+        <v>3932</v>
+      </c>
+      <c r="J36" s="3">
+        <v>5.44</v>
+      </c>
+      <c r="K36" s="3">
+        <v>5.383</v>
+      </c>
+      <c r="L36" s="3">
+        <v>6.1881000000000004</v>
+      </c>
+      <c r="M36" s="5">
+        <v>0.75490000000000002</v>
+      </c>
+      <c r="N36" s="6">
+        <v>591.25</v>
+      </c>
+      <c r="O36" s="6">
+        <v>1925</v>
+      </c>
+      <c r="P36" s="6">
+        <v>2345</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>1436.5</v>
+      </c>
+      <c r="R36" s="6">
+        <v>1436.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Supply Chain\Gestão\Reportes\Relatório Mensal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F725F3-1A0C-4A62-9E09-4A1E98AA893C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD4BE60-E543-4AAA-BEAF-7EBEC91B8D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19CE77E3-4AC1-43FA-889F-0CF0F915B873}"/>
   </bookViews>
@@ -522,18 +522,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D8CCE4-1984-402D-851F-C5F1CB7E5FA3}">
-  <dimension ref="A1:R36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R38"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="12.6640625" customWidth="1"/>
-    <col min="18" max="18" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="12.7265625" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="12.7265625" customWidth="1"/>
+    <col min="18" max="18" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,7 +589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>44927</v>
       </c>
@@ -635,7 +635,7 @@
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>44958</v>
       </c>
@@ -681,7 +681,7 @@
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>44986</v>
       </c>
@@ -727,7 +727,7 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>45017</v>
       </c>
@@ -773,7 +773,7 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>45047</v>
       </c>
@@ -819,7 +819,7 @@
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>45078</v>
       </c>
@@ -865,7 +865,7 @@
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>45108</v>
       </c>
@@ -911,7 +911,7 @@
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>45139</v>
       </c>
@@ -957,7 +957,7 @@
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>45170</v>
       </c>
@@ -1003,7 +1003,7 @@
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>45200</v>
       </c>
@@ -1049,7 +1049,7 @@
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>45231</v>
       </c>
@@ -1095,7 +1095,7 @@
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>45261</v>
       </c>
@@ -1141,7 +1141,7 @@
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>45292</v>
       </c>
@@ -1190,7 +1190,7 @@
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>45323</v>
       </c>
@@ -1239,7 +1239,7 @@
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>45352</v>
       </c>
@@ -1288,7 +1288,7 @@
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
         <v>45383</v>
       </c>
@@ -1337,7 +1337,7 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>45413</v>
       </c>
@@ -1386,7 +1386,7 @@
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>45444</v>
       </c>
@@ -1435,7 +1435,7 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>45474</v>
       </c>
@@ -1484,7 +1484,7 @@
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>45505</v>
       </c>
@@ -1533,7 +1533,7 @@
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>45536</v>
       </c>
@@ -1582,7 +1582,7 @@
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>45566</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>4773</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>45597</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>5873</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <v>45627</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>5370</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>45658</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>45689</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>45717</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>45748</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
         <v>45778</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>3905</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" s="8">
         <v>45809</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>45839</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <v>45870</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <v>45901</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" s="8">
         <v>45931</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>45962</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>591.25</v>
       </c>
       <c r="O36" s="6">
-        <v>1925</v>
+        <v>1752.272727272727</v>
       </c>
       <c r="P36" s="6">
         <v>2345</v>
@@ -2364,6 +2364,118 @@
       </c>
       <c r="R36" s="6">
         <v>1436.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
+        <v>45992</v>
+      </c>
+      <c r="B37" s="3">
+        <v>940</v>
+      </c>
+      <c r="C37" s="3">
+        <v>1085</v>
+      </c>
+      <c r="D37" s="4">
+        <v>2990</v>
+      </c>
+      <c r="E37" s="3">
+        <v>1262.74</v>
+      </c>
+      <c r="F37" s="3">
+        <v>553.13</v>
+      </c>
+      <c r="G37" s="3">
+        <v>633.09</v>
+      </c>
+      <c r="H37" s="3">
+        <v>2550</v>
+      </c>
+      <c r="I37" s="3">
+        <v>3758</v>
+      </c>
+      <c r="J37" s="3">
+        <v>5.39</v>
+      </c>
+      <c r="K37" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="L37" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="M37" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="N37" s="6">
+        <v>591.25</v>
+      </c>
+      <c r="O37" s="6">
+        <v>1688.6944444444443</v>
+      </c>
+      <c r="P37" s="6">
+        <v>2632.5</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>1290</v>
+      </c>
+      <c r="R37" s="6">
+        <v>1292.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>46023</v>
+      </c>
+      <c r="B38" s="3">
+        <v>934.34</v>
+      </c>
+      <c r="C38" s="3">
+        <v>1100</v>
+      </c>
+      <c r="D38" s="4">
+        <v>2990</v>
+      </c>
+      <c r="E38" s="3">
+        <v>1268.3</v>
+      </c>
+      <c r="F38" s="3">
+        <v>537.14</v>
+      </c>
+      <c r="G38" s="3">
+        <v>679.62</v>
+      </c>
+      <c r="H38" s="3">
+        <v>2584</v>
+      </c>
+      <c r="I38" s="3">
+        <v>3818</v>
+      </c>
+      <c r="J38" s="3">
+        <v>5.48</v>
+      </c>
+      <c r="K38" s="3">
+        <v>5.42</v>
+      </c>
+      <c r="L38" s="3">
+        <v>6.35</v>
+      </c>
+      <c r="M38" s="5">
+        <v>0.77539999999999998</v>
+      </c>
+      <c r="N38" s="6">
+        <v>591.25</v>
+      </c>
+      <c r="O38" s="6">
+        <v>1104.8</v>
+      </c>
+      <c r="P38" s="6">
+        <v>1825.5</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>1290</v>
+      </c>
+      <c r="R38" s="6">
+        <v>1292.5</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Supply Chain\Gestão\Reportes\Relatório Mensal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD4BE60-E543-4AAA-BEAF-7EBEC91B8D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4F802D-DB8C-43C8-B2D0-F5B063F38551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19CE77E3-4AC1-43FA-889F-0CF0F915B873}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19CE77E3-4AC1-43FA-889F-0CF0F915B873}"/>
   </bookViews>
   <sheets>
     <sheet name="Final" sheetId="1" r:id="rId1"/>
@@ -188,9 +188,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -522,18 +522,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D8CCE4-1984-402D-851F-C5F1CB7E5FA3}">
-  <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="12.7265625" customWidth="1"/>
-    <col min="9" max="9" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="12.7265625" customWidth="1"/>
-    <col min="18" max="18" width="10.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="12.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,7 +589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>44927</v>
       </c>
@@ -635,7 +635,7 @@
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>44958</v>
       </c>
@@ -681,7 +681,7 @@
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>44986</v>
       </c>
@@ -727,7 +727,7 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>45017</v>
       </c>
@@ -773,7 +773,7 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>45047</v>
       </c>
@@ -819,7 +819,7 @@
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>45078</v>
       </c>
@@ -865,7 +865,7 @@
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>45108</v>
       </c>
@@ -911,7 +911,7 @@
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>45139</v>
       </c>
@@ -957,7 +957,7 @@
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>45170</v>
       </c>
@@ -1003,7 +1003,7 @@
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>45200</v>
       </c>
@@ -1049,7 +1049,7 @@
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>45231</v>
       </c>
@@ -1095,7 +1095,7 @@
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>45261</v>
       </c>
@@ -1141,7 +1141,7 @@
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>45292</v>
       </c>
@@ -1190,7 +1190,7 @@
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>45323</v>
       </c>
@@ -1239,7 +1239,7 @@
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>45352</v>
       </c>
@@ -1288,7 +1288,7 @@
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>45383</v>
       </c>
@@ -1337,7 +1337,7 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>45413</v>
       </c>
@@ -1386,7 +1386,7 @@
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>45444</v>
       </c>
@@ -1435,7 +1435,7 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>45474</v>
       </c>
@@ -1484,7 +1484,7 @@
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>45505</v>
       </c>
@@ -1533,7 +1533,7 @@
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>45536</v>
       </c>
@@ -1582,7 +1582,7 @@
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>45566</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>4773</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>45597</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>5873</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>45627</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>5370</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>45658</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>45689</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>45717</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>45748</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>45778</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>3905</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>45809</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>45839</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>45870</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>45901</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>45931</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>45962</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>1436.5</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>45992</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>1292.5</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>46023</v>
       </c>
@@ -2476,6 +2476,62 @@
       </c>
       <c r="R38" s="6">
         <v>1292.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="8">
+        <v>46054</v>
+      </c>
+      <c r="B39" s="3">
+        <v>968.7</v>
+      </c>
+      <c r="C39" s="3">
+        <v>1128.3399999999999</v>
+      </c>
+      <c r="D39" s="4">
+        <v>2990</v>
+      </c>
+      <c r="E39" s="3">
+        <v>1179.6500000000001</v>
+      </c>
+      <c r="F39" s="3">
+        <v>541.44000000000005</v>
+      </c>
+      <c r="G39" s="3">
+        <v>684.04</v>
+      </c>
+      <c r="H39" s="3">
+        <v>2590</v>
+      </c>
+      <c r="I39" s="3">
+        <v>3660</v>
+      </c>
+      <c r="J39" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="K39" s="3">
+        <v>5.26</v>
+      </c>
+      <c r="L39" s="3">
+        <v>6.17</v>
+      </c>
+      <c r="M39" s="5">
+        <v>0.75760000000000005</v>
+      </c>
+      <c r="N39" s="6">
+        <v>591.25</v>
+      </c>
+      <c r="O39" s="6">
+        <v>1046.4000000000001</v>
+      </c>
+      <c r="P39" s="6">
+        <v>1825.5</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>969.5</v>
+      </c>
+      <c r="R39" s="6">
+        <v>969.5</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Supply Chain\Gestão\Reportes\Relatório Mensal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4F802D-DB8C-43C8-B2D0-F5B063F38551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DA83EC-352F-49AD-AE66-96A9D1A48560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19CE77E3-4AC1-43FA-889F-0CF0F915B873}"/>
   </bookViews>
@@ -522,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D8CCE4-1984-402D-851F-C5F1CB7E5FA3}">
-  <dimension ref="A1:R39"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2534,6 +2534,106 @@
         <v>969.5</v>
       </c>
     </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" s="8">
+        <v>46082</v>
+      </c>
+      <c r="B40" s="3">
+        <v>1061.3599999999999</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1251</v>
+      </c>
+      <c r="D40" s="4">
+        <v>2990</v>
+      </c>
+      <c r="E40" s="3">
+        <v>1124.08</v>
+      </c>
+      <c r="F40" s="3">
+        <v>601.70000000000005</v>
+      </c>
+      <c r="G40" s="3">
+        <v>700.73</v>
+      </c>
+      <c r="H40" s="3">
+        <v>2681</v>
+      </c>
+      <c r="I40" s="3">
+        <v>3670</v>
+      </c>
+      <c r="J40" s="3">
+        <v>5.32</v>
+      </c>
+      <c r="K40" s="3">
+        <v>5.21</v>
+      </c>
+      <c r="L40" s="3">
+        <v>6.05</v>
+      </c>
+      <c r="M40" s="5">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="N40" s="6">
+        <v>543.75</v>
+      </c>
+      <c r="O40" s="6">
+        <v>3430</v>
+      </c>
+      <c r="P40" s="6">
+        <v>1250</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>987.5</v>
+      </c>
+      <c r="R40" s="6">
+        <v>1192.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" s="8">
+        <v>46113</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1107</v>
+      </c>
+      <c r="C41" s="3">
+        <v>1280</v>
+      </c>
+      <c r="D41" s="4">
+        <v>2990</v>
+      </c>
+      <c r="E41">
+        <f>E40*1.76</f>
+        <v>1978.3807999999999</v>
+      </c>
+      <c r="F41">
+        <f>F40*1.3188</f>
+        <v>793.52196000000004</v>
+      </c>
+      <c r="G41">
+        <f>G40*1.32</f>
+        <v>924.96360000000004</v>
+      </c>
+      <c r="H41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I41" s="3">
+        <v>3950</v>
+      </c>
+      <c r="J41" s="3">
+        <v>5.25</v>
+      </c>
+      <c r="K41" s="3">
+        <v>5.18</v>
+      </c>
+      <c r="L41" s="3">
+        <v>5.99</v>
+      </c>
+      <c r="M41" s="5">
+        <v>0.75129999999999997</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Supply Chain\Gestão\Reportes\Relatório Mensal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DA83EC-352F-49AD-AE66-96A9D1A48560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0F03FA-3679-4C18-BB25-894B15486567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19CE77E3-4AC1-43FA-889F-0CF0F915B873}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{19CE77E3-4AC1-43FA-889F-0CF0F915B873}"/>
   </bookViews>
   <sheets>
     <sheet name="Final" sheetId="1" r:id="rId1"/>
@@ -522,18 +522,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D8CCE4-1984-402D-851F-C5F1CB7E5FA3}">
-  <dimension ref="A1:R41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="12.7109375" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="12.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="12.6640625" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,7 +589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>44927</v>
       </c>
@@ -635,7 +635,7 @@
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>44958</v>
       </c>
@@ -681,7 +681,7 @@
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>44986</v>
       </c>
@@ -727,7 +727,7 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>45017</v>
       </c>
@@ -773,7 +773,7 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>45047</v>
       </c>
@@ -819,7 +819,7 @@
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>45078</v>
       </c>
@@ -865,7 +865,7 @@
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>45108</v>
       </c>
@@ -911,7 +911,7 @@
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>45139</v>
       </c>
@@ -957,7 +957,7 @@
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>45170</v>
       </c>
@@ -1003,7 +1003,7 @@
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>45200</v>
       </c>
@@ -1049,7 +1049,7 @@
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>45231</v>
       </c>
@@ -1095,7 +1095,7 @@
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>45261</v>
       </c>
@@ -1141,7 +1141,7 @@
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>45292</v>
       </c>
@@ -1190,7 +1190,7 @@
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>45323</v>
       </c>
@@ -1239,7 +1239,7 @@
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>45352</v>
       </c>
@@ -1288,7 +1288,7 @@
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>45383</v>
       </c>
@@ -1337,7 +1337,7 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>45413</v>
       </c>
@@ -1386,7 +1386,7 @@
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>45444</v>
       </c>
@@ -1435,7 +1435,7 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>45474</v>
       </c>
@@ -1484,7 +1484,7 @@
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>45505</v>
       </c>
@@ -1533,7 +1533,7 @@
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>45536</v>
       </c>
@@ -1582,7 +1582,7 @@
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>45566</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>4773</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>45597</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>5873</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>45627</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>5370</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>45658</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>45689</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>45717</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>45748</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>45778</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>3905</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>45809</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>45839</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>45870</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>45901</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>45931</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>45962</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>1436.5</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>45992</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>1292.5</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>46023</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>1292.5</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>46054</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>969.5</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>46082</v>
       </c>
@@ -2590,28 +2590,28 @@
         <v>1192.5</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>46113</v>
       </c>
       <c r="B41" s="3">
-        <v>1107</v>
+        <v>1123.99</v>
       </c>
       <c r="C41" s="3">
-        <v>1280</v>
+        <v>1295</v>
       </c>
       <c r="D41" s="4">
         <v>2990</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="3">
         <f>E40*1.76</f>
         <v>1978.3807999999999</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="3">
         <f>F40*1.3188</f>
         <v>793.52196000000004</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="3">
         <f>G40*1.32</f>
         <v>924.96360000000004</v>
       </c>
@@ -2632,6 +2632,77 @@
       </c>
       <c r="M41" s="5">
         <v>0.75129999999999997</v>
+      </c>
+      <c r="N41" s="6">
+        <v>563.75</v>
+      </c>
+      <c r="O41" s="6">
+        <v>2444.416666666667</v>
+      </c>
+      <c r="P41" s="6">
+        <v>2785</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>1735</v>
+      </c>
+      <c r="R41" s="6">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42" s="8">
+        <v>46143</v>
+      </c>
+      <c r="B42" s="3">
+        <v>1144.67</v>
+      </c>
+      <c r="C42" s="3">
+        <v>1340.26</v>
+      </c>
+      <c r="D42" s="4">
+        <v>3100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2166.34</v>
+      </c>
+      <c r="F42" s="3">
+        <v>1027.22</v>
+      </c>
+      <c r="G42" s="3">
+        <v>1111.3399999999999</v>
+      </c>
+      <c r="H42" s="3">
+        <v>3777</v>
+      </c>
+      <c r="I42" s="3">
+        <v>4340</v>
+      </c>
+      <c r="J42" s="3">
+        <v>5.05</v>
+      </c>
+      <c r="K42" s="3">
+        <v>4.95</v>
+      </c>
+      <c r="L42" s="3">
+        <v>5.81</v>
+      </c>
+      <c r="M42" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="N42" s="6">
+        <v>563.75</v>
+      </c>
+      <c r="O42" s="6">
+        <v>2460.67</v>
+      </c>
+      <c r="P42" s="6">
+        <v>2674.5</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>1798.5</v>
+      </c>
+      <c r="R42" s="6">
+        <v>1798.5</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Supply Chain\Gestão\Reportes\Relatório Mensal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0F03FA-3679-4C18-BB25-894B15486567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464FEF75-8F03-4A0D-8D19-865053790A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{19CE77E3-4AC1-43FA-889F-0CF0F915B873}"/>
+    <workbookView xWindow="-19310" yWindow="-140" windowWidth="19420" windowHeight="11500" xr2:uid="{19CE77E3-4AC1-43FA-889F-0CF0F915B873}"/>
   </bookViews>
   <sheets>
     <sheet name="Final" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -188,9 +188,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -522,18 +522,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D8CCE4-1984-402D-851F-C5F1CB7E5FA3}">
-  <dimension ref="A1:R42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="17" width="12.6640625" customWidth="1"/>
-    <col min="18" max="18" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="17" width="12.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,7 +589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>44927</v>
       </c>
@@ -635,7 +635,7 @@
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>44958</v>
       </c>
@@ -681,7 +681,7 @@
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>44986</v>
       </c>
@@ -727,7 +727,7 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>45017</v>
       </c>
@@ -773,7 +773,7 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>45047</v>
       </c>
@@ -819,7 +819,7 @@
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>45078</v>
       </c>
@@ -865,7 +865,7 @@
       <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>45108</v>
       </c>
@@ -911,7 +911,7 @@
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>45139</v>
       </c>
@@ -957,7 +957,7 @@
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>45170</v>
       </c>
@@ -1003,7 +1003,7 @@
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>45200</v>
       </c>
@@ -1049,7 +1049,7 @@
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>45231</v>
       </c>
@@ -1095,7 +1095,7 @@
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>45261</v>
       </c>
@@ -1141,7 +1141,7 @@
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>45292</v>
       </c>
@@ -1190,7 +1190,7 @@
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>45323</v>
       </c>
@@ -1239,7 +1239,7 @@
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>45352</v>
       </c>
@@ -1288,7 +1288,7 @@
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>45383</v>
       </c>
@@ -1337,7 +1337,7 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>45413</v>
       </c>
@@ -1386,7 +1386,7 @@
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>45444</v>
       </c>
@@ -1435,7 +1435,7 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>45474</v>
       </c>
@@ -1484,7 +1484,7 @@
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>45505</v>
       </c>
@@ -1533,7 +1533,7 @@
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>45536</v>
       </c>
@@ -1582,7 +1582,7 @@
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>45566</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>4773</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>45597</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>5873</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>45627</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>5370</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>45658</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>45689</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>45717</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>45748</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <v>45778</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>3905</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>45809</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>45839</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>45870</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>45901</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>45931</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <v>45962</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>1436.5</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>45992</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>1292.5</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
         <v>46023</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>1292.5</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
         <v>46054</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>969.5</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>46082</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>1192.5</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>46113</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>46143</v>
       </c>
@@ -2703,6 +2703,62 @@
       </c>
       <c r="R42" s="6">
         <v>1798.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
+        <v>46174</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1190</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1380</v>
+      </c>
+      <c r="D43" s="4">
+        <v>3100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1403.625</v>
+      </c>
+      <c r="F43" s="3">
+        <v>791.06567999999993</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1461.204</v>
+      </c>
+      <c r="H43" s="3">
+        <v>3604</v>
+      </c>
+      <c r="I43" s="3">
+        <v>4080</v>
+      </c>
+      <c r="J43" s="3">
+        <v>4.9964699999999995</v>
+      </c>
+      <c r="K43" s="3">
+        <v>5</v>
+      </c>
+      <c r="L43" s="3">
+        <v>5.88</v>
+      </c>
+      <c r="M43" s="5">
+        <v>0.73</v>
+      </c>
+      <c r="N43" s="6">
+        <v>563.75</v>
+      </c>
+      <c r="O43" s="6">
+        <v>6770</v>
+      </c>
+      <c r="P43" s="6">
+        <v>2674.5</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>2199.5</v>
+      </c>
+      <c r="R43" s="6">
+        <v>2212</v>
       </c>
     </row>
   </sheetData>
